--- a/Hoc_caohoc/hoso_caohoc/CTDT.xlsx
+++ b/Hoc_caohoc/hoso_caohoc/CTDT.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="165">
   <si>
     <t>KHUNG CHƯƠNG TRÌNH ĐÀO TẠO TRÌNH ĐỘ THẠC SĨ</t>
   </si>
@@ -592,6 +592,9 @@
   </si>
   <si>
     <t>Trường Đại học công nghệ Đông Á</t>
+  </si>
+  <si>
+    <t>cô kt, thủy lợi: 0982591396</t>
   </si>
 </sst>
 </file>
@@ -1038,6 +1041,31 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
@@ -1045,31 +1073,7 @@
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1077,31 +1081,30 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1401,80 +1404,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="C5" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="67" t="s">
+      <c r="D5" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="67"/>
-      <c r="F5" s="59" t="s">
+      <c r="E5" s="65"/>
+      <c r="F5" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="59" t="s">
+      <c r="G5" s="62" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" ht="28.5">
-      <c r="A6" s="59"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
       <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" ht="22.5" customHeight="1">
       <c r="A7" s="4" t="s">
@@ -1564,13 +1567,13 @@
       <c r="A11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
       <c r="G11" s="13" t="s">
         <v>26</v>
       </c>
@@ -1579,13 +1582,13 @@
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="60" t="s">
+      <c r="B12" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
       <c r="G12" s="14">
         <v>9</v>
       </c>
@@ -1663,13 +1666,13 @@
       <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="60" t="s">
+      <c r="B16" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
       <c r="G16" s="13" t="s">
         <v>39</v>
       </c>
@@ -1908,13 +1911,13 @@
       <c r="A27" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="60" t="s">
+      <c r="B27" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
       <c r="G27" s="14">
         <v>23</v>
       </c>
@@ -1923,13 +1926,13 @@
       <c r="A28" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="60" t="s">
+      <c r="B28" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="60"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
       <c r="G28" s="14">
         <v>15</v>
       </c>
@@ -2053,13 +2056,13 @@
       <c r="A34" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="60" t="s">
+      <c r="B34" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="C34" s="60"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="60"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="68"/>
       <c r="G34" s="14">
         <v>8</v>
       </c>
@@ -2243,24 +2246,24 @@
       </c>
     </row>
     <row r="43" spans="1:8" s="2" customFormat="1" ht="21" customHeight="1">
-      <c r="A43" s="59" t="s">
+      <c r="A43" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="59"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
+      <c r="B43" s="62"/>
+      <c r="C43" s="62"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
+      <c r="F43" s="62"/>
       <c r="G43" s="14">
         <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="2" customFormat="1"/>
     <row r="45" spans="1:8" s="2" customFormat="1">
-      <c r="B45" s="57">
+      <c r="B45" s="66">
         <v>268119167</v>
       </c>
-      <c r="C45" s="58"/>
+      <c r="C45" s="67"/>
       <c r="D45" s="56" t="s">
         <v>112</v>
       </c>
@@ -2279,7 +2282,7 @@
       <c r="B48" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C48" s="78" t="s">
+      <c r="C48" s="57" t="s">
         <v>162</v>
       </c>
     </row>
@@ -2287,12 +2290,16 @@
       <c r="C49"/>
     </row>
     <row r="50" spans="3:3" s="2" customFormat="1">
-      <c r="C50" s="78" t="s">
+      <c r="C50" s="57" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="51" spans="3:3" s="2" customFormat="1"/>
-    <row r="52" spans="3:3" s="2" customFormat="1"/>
+    <row r="52" spans="3:3" s="2" customFormat="1">
+      <c r="C52" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
     <row r="53" spans="3:3" s="2" customFormat="1"/>
     <row r="54" spans="3:3" s="2" customFormat="1"/>
     <row r="55" spans="3:3" s="2" customFormat="1"/>
@@ -2343,6 +2350,14 @@
     <row r="100" s="2" customFormat="1"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B34:F34"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
@@ -2353,14 +2368,6 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="G5:G6"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B34:F34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2823,10 +2830,10 @@
       <c r="A13" s="52" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="C13" s="69"/>
+      <c r="C13" s="70"/>
       <c r="D13" s="46"/>
       <c r="E13" s="53">
         <v>1</v>
@@ -2851,10 +2858,10 @@
       <c r="A14" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="B14" s="68" t="s">
+      <c r="B14" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="69"/>
+      <c r="C14" s="70"/>
       <c r="D14" s="46"/>
       <c r="E14" s="53">
         <v>2</v>
@@ -2879,10 +2886,10 @@
       <c r="A15" s="52" t="s">
         <v>148</v>
       </c>
-      <c r="B15" s="68" t="s">
+      <c r="B15" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="C15" s="69"/>
+      <c r="C15" s="70"/>
       <c r="D15" s="46"/>
       <c r="E15" s="53">
         <v>3</v>
@@ -2907,10 +2914,10 @@
       <c r="A16" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="B16" s="68" t="s">
+      <c r="B16" s="69" t="s">
         <v>153</v>
       </c>
-      <c r="C16" s="69"/>
+      <c r="C16" s="70"/>
       <c r="D16" s="46"/>
       <c r="E16" s="53">
         <v>4</v>
@@ -2935,10 +2942,10 @@
       <c r="A17" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="69" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="69"/>
+      <c r="C17" s="70"/>
       <c r="D17" s="46"/>
       <c r="E17" s="46"/>
       <c r="F17" s="46"/>
@@ -2955,10 +2962,10 @@
       <c r="A18" s="52" t="s">
         <v>157</v>
       </c>
-      <c r="B18" s="68" t="s">
+      <c r="B18" s="69" t="s">
         <v>158</v>
       </c>
-      <c r="C18" s="69"/>
+      <c r="C18" s="70"/>
       <c r="D18" s="46"/>
       <c r="E18" s="46"/>
       <c r="F18" s="46"/>
@@ -2972,11 +2979,11 @@
       <c r="N18" s="46"/>
     </row>
     <row r="19" spans="1:14" ht="66" customHeight="1">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="78"/>
       <c r="D19" s="46"/>
       <c r="E19" s="46"/>
       <c r="F19" s="46"/>
@@ -2991,17 +2998,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A2:A9"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="A19:C19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Hoc_caohoc/hoso_caohoc/CTDT.xlsx
+++ b/Hoc_caohoc/hoso_caohoc/CTDT.xlsx
@@ -16,6 +16,7 @@
     <sheet name="DkyHKI" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
